--- a/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
+++ b/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
@@ -47,6 +47,180 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-06-05 22:29:14]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 08:33:01]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 10:14:31]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 10:19:09]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 10:21:24]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 10:23:55]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 10:41:48]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@START_INFO ZRS240929001A:DESKTOP-M5HPH95:HM:RS70B64G4M08G:E9002B:AE35:FT3_RS70B64G4M08G_032003003_032003003::3040:::FT::R80544:FT3:FT:25+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@INFO_OK+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 11:15:42]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 11:20:41]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 11:36:13]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;开始时间:2025-06-06 11:35:45.777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;按下结批时间:2025-06-06 11:35:45.777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;结批时间:00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;结束时间:2025-06-06 11:35:45.777</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;运行时间:00:00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;UPH:0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;载入数:0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;总计:0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Auto1:0,良率:NaN%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Auto2:0,良率:NaN%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Fix1:0,良率:NaN%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Fix2:0,良率:NaN%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Fix3:0,良率:NaN%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 11:41:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;开始时间:2025-06-06 11:41:09.969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;按下结批时间:2025-06-06 11:41:09.969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;结束时间:2025-06-06 11:41:09.969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;UPH:-2147483648</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;总计:15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Auto1:1,良率:6.7%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Auto2:2,良率: 13.3%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Fix1:3,良率: 20.0%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Fix2:4,良率: 26.7%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;Fix3:5,良率: 33.3%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 11:48:41]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;开始时间:2025-06-06 11:48:12.797</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;按下结批时间:2025-06-06 11:48:12.797</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PS结批流程.StepID=500-&gt;结束时间:2025-06-06 11:48:12.797</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 12:44:05]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 13:46:10]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 13:48:53]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 14:04:13]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
@@ -498,6 +672,1168 @@
         <x:v>9</x:v>
       </x:c>
     </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="1">
+        <x:v>45814.3562886574</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:4">
+      <x:c r="A8" s="1">
+        <x:v>45814.3562899653</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="1">
+        <x:v>45814.4267696065</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="1">
+        <x:v>45814.426773044</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="1">
+        <x:v>45814.4299828241</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="1">
+        <x:v>45814.4299847569</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:4">
+      <x:c r="A13" s="1">
+        <x:v>45814.4315546412</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:4">
+      <x:c r="A14" s="1">
+        <x:v>45814.4315567593</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:4">
+      <x:c r="A15" s="1">
+        <x:v>45814.4333041088</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:4">
+      <x:c r="A16" s="1">
+        <x:v>45814.4333071065</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:4">
+      <x:c r="A17" s="1">
+        <x:v>45814.4457164236</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:4">
+      <x:c r="A18" s="1">
+        <x:v>45814.4457195486</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:4">
+      <x:c r="A19" s="1">
+        <x:v>45814.4463863194</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:4">
+      <x:c r="A20" s="1">
+        <x:v>45814.4463875926</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:4">
+      <x:c r="A21" s="1">
+        <x:v>45814.469259375</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:4">
+      <x:c r="A22" s="1">
+        <x:v>45814.469260706</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:4">
+      <x:c r="A23" s="1">
+        <x:v>45814.4697803588</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:4">
+      <x:c r="A24" s="1">
+        <x:v>45814.4697828704</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:4">
+      <x:c r="A25" s="1">
+        <x:v>45814.4727180208</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:4">
+      <x:c r="A26" s="1">
+        <x:v>45814.4727199306</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="1">
+        <x:v>45814.4729620139</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="1">
+        <x:v>45814.4729632639</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="1">
+        <x:v>45814.4835090625</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="1">
+        <x:v>45814.4835110185</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="1">
+        <x:v>45814.4836485069</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="1">
+        <x:v>45814.4836497801</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="1">
+        <x:v>45814.4852625347</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="1">
+        <x:v>45814.4852639583</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="1">
+        <x:v>45814.4852652662</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="1">
+        <x:v>45814.4852665046</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="1">
+        <x:v>45814.4852677778</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="1">
+        <x:v>45814.4852690509</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="1">
+        <x:v>45814.4852704514</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="1">
+        <x:v>45814.4852717824</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="1">
+        <x:v>45814.485273044</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="1">
+        <x:v>45814.4852743171</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="1">
+        <x:v>45814.485275625</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="1">
+        <x:v>45814.4852768287</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="1">
+        <x:v>45814.485278125</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="1">
+        <x:v>45814.4872487847</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="1">
+        <x:v>45814.4872522454</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D47" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="1">
+        <x:v>45814.4873553472</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="1">
+        <x:v>45814.4873565972</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="1">
+        <x:v>45814.4875181597</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="1">
+        <x:v>45814.4875195602</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="1">
+        <x:v>45814.4875208449</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4">
+      <x:c r="A53" s="1">
+        <x:v>45814.4875221181</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4">
+      <x:c r="A54" s="1">
+        <x:v>45814.4875234607</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:4">
+      <x:c r="A55" s="1">
+        <x:v>45814.4875246759</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:4">
+      <x:c r="A56" s="1">
+        <x:v>45814.4875259606</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:4">
+      <x:c r="A57" s="1">
+        <x:v>45814.4875272222</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:4">
+      <x:c r="A58" s="1">
+        <x:v>45814.4875284954</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:4">
+      <x:c r="A59" s="1">
+        <x:v>45814.4875298032</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:4">
+      <x:c r="A60" s="1">
+        <x:v>45814.4875310532</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:4">
+      <x:c r="A61" s="1">
+        <x:v>45814.4875323148</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:4">
+      <x:c r="A62" s="1">
+        <x:v>45814.487533588</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:4">
+      <x:c r="A63" s="1">
+        <x:v>45814.4921562269</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:4">
+      <x:c r="A64" s="1">
+        <x:v>45814.4921581713</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D64" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:4">
+      <x:c r="A65" s="1">
+        <x:v>45814.4922025694</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:4">
+      <x:c r="A66" s="1">
+        <x:v>45814.4922038773</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:4">
+      <x:c r="A67" s="1">
+        <x:v>45814.4939166782</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:4">
+      <x:c r="A68" s="1">
+        <x:v>45814.4939180324</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:4">
+      <x:c r="A69" s="1">
+        <x:v>45814.4939194329</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:4">
+      <x:c r="A70" s="1">
+        <x:v>45814.4939207176</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:4">
+      <x:c r="A71" s="1">
+        <x:v>45814.4939219907</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:4">
+      <x:c r="A72" s="1">
+        <x:v>45814.4939234144</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:4">
+      <x:c r="A73" s="1">
+        <x:v>45814.4939248843</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:4">
+      <x:c r="A74" s="1">
+        <x:v>45814.4939261574</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:4">
+      <x:c r="A75" s="1">
+        <x:v>45814.4939274074</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:4">
+      <x:c r="A76" s="1">
+        <x:v>45814.493928669</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:4">
+      <x:c r="A77" s="1">
+        <x:v>45814.4939299537</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:4">
+      <x:c r="A78" s="1">
+        <x:v>45814.4939312269</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:4">
+      <x:c r="A79" s="1">
+        <x:v>45814.4939325116</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:4">
+      <x:c r="A80" s="1">
+        <x:v>45814.5306395949</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:4">
+      <x:c r="A81" s="1">
+        <x:v>45814.5306414583</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D81" s="2" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:4">
+      <x:c r="A82" s="1">
+        <x:v>45814.5313010995</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:4">
+      <x:c r="A83" s="1">
+        <x:v>45814.5313023495</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:4">
+      <x:c r="A84" s="1">
+        <x:v>45814.5737526273</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:4">
+      <x:c r="A85" s="1">
+        <x:v>45814.5737548148</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D85" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:4">
+      <x:c r="A86" s="1">
+        <x:v>45814.5756364583</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:4">
+      <x:c r="A87" s="1">
+        <x:v>45814.5756387268</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D87" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:4">
+      <x:c r="A88" s="1">
+        <x:v>45814.5862706829</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:4">
+      <x:c r="A89" s="1">
+        <x:v>45814.5862734954</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D89" s="2" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
+++ b/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
@@ -221,6 +221,439 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-06-06 14:04:13]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-06 23:17:42]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 10:57:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[测试超时时间]:600-&gt;601:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[timeout超时时间]:10-&gt;11:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[测试超时时间]:601-&gt;600:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[timeout超时时间]:11-&gt;10:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 13:59:01]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>密码9630000错误！</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 14:01:35]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 14:02:53]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 14:05:47]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 14:07:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 14:12:22]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 14:20:18]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:31:31]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:35:36]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:39:04]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:41:21]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:43:31]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:45:54]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:47:27]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:49:49]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:54:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:57:09]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 15:59:14]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:03:25]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:05:20]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:11:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:20:05]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:24:02]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:27:04]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:28:12]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:30:29]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:31:29]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:35:02]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:41:35]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:43:31]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:45:01]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:47:33]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:49:21]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 16:52:51]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 17:18:40]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>出料吸嘴_吸放料(System.Boolean[],True)未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>出料吸嘴_吸放料(System.Boolean[],False)未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 17:20:52]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>加热盘加热开启失败！未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Y134_Site7加热 开启失败！未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>密码852错误！</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 17:24:21]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 17:27:18]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 18:51:43]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 20:35:29]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 20:37:44]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 20:52:03]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-07 20:57:31]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 09:19:10]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 09:19:39]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：update DutCurrent set pass=0,total=0,usedTime=0，错误信息：SQL logic error
+no such table: DutCurrent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 10:07:51]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 10:27:05]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 10:28:48]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 10:30:26]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 10:33:46]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 10:35:44]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：create table f_ZRS240929001A_20250609_10_26_46(批次开始日期 nvarchar(50) NULL,获取MAP时间 nvarchar(50) NULL,料号 nvarchar(50) NULL,批号 nvarchar(20) NULL,MAP信息 nvarchar(50) NULL )，错误信息：数据库中已存在名为 'f_ZRS240929001A_20250609_10_26_46' 的对象。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：create table o_ZRS240929001A_20250609_10_26_46(时间 nvarchar(50) NULL,名称 nvarchar(50) NULL,大小 nvarchar(50) NULL,数据 nvarchar(MAX) NULL)，错误信息：数据库中已存在名为 'o_ZRS240929001A_20250609_10_26_46' 的对象。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：insert into f_ZRS240929001A_20250609_10_35_26(批次开始日期,获取MAP时间,料号,批号,MAP信息)values('2025年6月9日','2025/6/9 10:36:15','RS70B64G4M08G','E9002B','@TEST_DONE 00 01 01 01 01 01 01 01 01')，错误信息：对象名 'f_ZRS240929001A_20250609_10_35_26' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 10:49:06]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]1400330,[Msg]创建MAP信息数据库失败!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]1400330,[Msg]创建BIN信息数据库失败!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 11:09:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 11:17:25]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 11:31:06]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：insert into o__20250609_11_30_47(时间,名称,大小,数据) values('2025/6/9 11:31:06','auto2','8x19','00,01,02,03,04,05,06,07,08,09,010,011,012,013,014,015,016,017,018,10,11,12,13,14,15,16,17,18,19,110,111,112,113,114,115,116,117,118,20,21,22,23,24,25,26,27,28,29,210,211,212,213,214,215,216,217,218,30,31,32,33,34,35,36,37,38,39,310,311,312,313,314,315,316,317,318,40,41,42,43,44,45,46,47,48,49,410,411,412,413,414,415,416,417,418,50,51,52,53,54,55,56,57,58,59,510,511,512,513,514,515,516,517,518,60,61,62,63,64,65,66,67,68,69,610,611,612,613,614,615,616,617,618,70,71,72,73,74,75,76,77,78,79,710,711,712,713,714,715,716,717,718')，错误信息：对象名 'o__20250609_11_30_47' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：insert into o__20250609_11_30_47(时间,名称,大小,数据) values('2025/6/9 11:31:06','fix1','8x19','00,01,02,03,04,05,06,07,08,09,010,011,012,013,014,015,016,017,018,10,11,12,13,14,15,16,17,18,19,110,111,112,113,114,115,116,117,118,20,21,22,23,24,25,26,27,28,29,210,211,212,213,214,215,216,217,218,30,31,32,33,34,35,36,37,38,39,310,311,312,313,314,315,316,317,318,40,41,42,43,44,45,46,47,48,49,410,411,412,413,414,415,416,417,418,50,51,52,53,54,55,56,57,58,59,510,511,512,513,514,515,516,517,518,60,61,62,63,64,65,66,67,68,69,610,611,612,613,614,615,616,617,618,70,71,72,73,74,75,76,77,78,79,710,711,712,713,714,715,716,717,718')，错误信息：对象名 'o__20250609_11_30_47' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：insert into o__20250609_11_30_47(时间,名称,大小,数据) values('2025/6/9 11:31:06','fix2','8x19','00,01,02,03,04,05,06,07,08,09,010,011,012,013,014,015,016,017,018,10,11,12,13,14,15,16,17,18,19,110,111,112,113,114,115,116,117,118,20,21,22,23,24,25,26,27,28,29,210,211,212,213,214,215,216,217,218,30,31,32,33,34,35,36,37,38,39,310,311,312,313,314,315,316,317,318,40,41,42,43,44,45,46,47,48,49,410,411,412,413,414,415,416,417,418,50,51,52,53,54,55,56,57,58,59,510,511,512,513,514,515,516,517,518,60,61,62,63,64,65,66,67,68,69,610,611,612,613,614,615,616,617,618,70,71,72,73,74,75,76,77,78,79,710,711,712,713,714,715,716,717,718')，错误信息：对象名 'o__20250609_11_30_47' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 11:36:03]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：insert into o__20250609_11_35_36(时间,名称,大小,数据) values('2025/6/9 11:36:40','auto2','8x19','00,01,02,03,04,05,06,07,08,09,010,011,012,013,014,015,016,017,018,10,11,12,13,14,15,16,17,18,19,110,111,112,113,114,115,116,117,118,20,21,22,23,24,25,26,27,28,29,210,211,212,213,214,215,216,217,218,30,31,32,33,34,35,36,37,38,39,310,311,312,313,314,315,316,317,318,40,41,42,43,44,45,46,47,48,49,410,411,412,413,414,415,416,417,418,50,51,52,53,54,55,56,57,58,59,510,511,512,513,514,515,516,517,518,60,61,62,63,64,65,66,67,68,69,610,611,612,613,614,615,616,617,618,70,71,72,73,74,75,76,77,78,79,710,711,712,713,714,715,716,717,718')，错误信息：对象名 'o__20250609_11_35_36' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 11:40:16]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 12:19:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 12:43:55]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 12:49:35]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
@@ -1834,6 +2267,2442 @@
         <x:v>52</x:v>
       </x:c>
     </x:row>
+    <x:row r="90" spans="1:4">
+      <x:c r="A90" s="1">
+        <x:v>45814.9706323843</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:4">
+      <x:c r="A91" s="1">
+        <x:v>45814.9706325926</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D91" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:4">
+      <x:c r="A92" s="1">
+        <x:v>45815.4566817824</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:4">
+      <x:c r="A93" s="1">
+        <x:v>45815.4566819907</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D93" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:4">
+      <x:c r="A94" s="1">
+        <x:v>45815.4573745602</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:4">
+      <x:c r="A95" s="1">
+        <x:v>45815.4573745602</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:4">
+      <x:c r="A96" s="1">
+        <x:v>45815.4576966898</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:4">
+      <x:c r="A97" s="1">
+        <x:v>45815.4576966898</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:4">
+      <x:c r="A98" s="1">
+        <x:v>45815.5826573032</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:4">
+      <x:c r="A99" s="1">
+        <x:v>45815.5826575926</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D99" s="2" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:4">
+      <x:c r="A100" s="1">
+        <x:v>45815.583050544</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:4">
+      <x:c r="A101" s="1">
+        <x:v>45815.5844331019</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:4">
+      <x:c r="A102" s="1">
+        <x:v>45815.5844333681</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D102" s="2" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:4">
+      <x:c r="A103" s="1">
+        <x:v>45815.5853466204</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:4">
+      <x:c r="A104" s="1">
+        <x:v>45815.585346956</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D104" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:4">
+      <x:c r="A105" s="1">
+        <x:v>45815.5873600116</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:4">
+      <x:c r="A106" s="1">
+        <x:v>45815.5873602778</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D106" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:4">
+      <x:c r="A107" s="1">
+        <x:v>45815.5886261921</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:4">
+      <x:c r="A108" s="1">
+        <x:v>45815.5886263657</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D108" s="2" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:4">
+      <x:c r="A109" s="1">
+        <x:v>45815.5919223958</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:4">
+      <x:c r="A110" s="1">
+        <x:v>45815.5919225926</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D110" s="2" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:4">
+      <x:c r="A111" s="1">
+        <x:v>45815.5974394676</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:4">
+      <x:c r="A112" s="1">
+        <x:v>45815.5974396528</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D112" s="2" t="s">
+        <x:v>66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:4">
+      <x:c r="A113" s="1">
+        <x:v>45815.646897419</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:4">
+      <x:c r="A114" s="1">
+        <x:v>45815.646897581</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D114" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:4">
+      <x:c r="A115" s="1">
+        <x:v>45815.6497218866</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:4">
+      <x:c r="A116" s="1">
+        <x:v>45815.6497222569</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D116" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:4">
+      <x:c r="A117" s="1">
+        <x:v>45815.6521341898</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:4">
+      <x:c r="A118" s="1">
+        <x:v>45815.6521343634</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D118" s="2" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:4">
+      <x:c r="A119" s="1">
+        <x:v>45815.6537251736</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:4">
+      <x:c r="A120" s="1">
+        <x:v>45815.6537255556</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D120" s="2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:4">
+      <x:c r="A121" s="1">
+        <x:v>45815.6552221528</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:4">
+      <x:c r="A122" s="1">
+        <x:v>45815.6552223264</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D122" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:4">
+      <x:c r="A123" s="1">
+        <x:v>45815.6568823727</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:4">
+      <x:c r="A124" s="1">
+        <x:v>45815.6568825579</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D124" s="2" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:4">
+      <x:c r="A125" s="1">
+        <x:v>45815.6579589005</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:4">
+      <x:c r="A126" s="1">
+        <x:v>45815.6579590741</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D126" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:4">
+      <x:c r="A127" s="1">
+        <x:v>45815.6596023611</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:4">
+      <x:c r="A128" s="1">
+        <x:v>45815.6596025579</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D128" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:4">
+      <x:c r="A129" s="1">
+        <x:v>45815.6629290972</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:4">
+      <x:c r="A130" s="1">
+        <x:v>45815.6629292708</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D130" s="2" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:4">
+      <x:c r="A131" s="1">
+        <x:v>45815.6646951273</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:4">
+      <x:c r="A132" s="1">
+        <x:v>45815.6646954861</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D132" s="2" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:4">
+      <x:c r="A133" s="1">
+        <x:v>45815.6661415741</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:4">
+      <x:c r="A134" s="1">
+        <x:v>45815.6661417593</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D134" s="2" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:4">
+      <x:c r="A135" s="1">
+        <x:v>45815.6690425</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:4">
+      <x:c r="A136" s="1">
+        <x:v>45815.6690426852</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D136" s="2" t="s">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:4">
+      <x:c r="A137" s="1">
+        <x:v>45815.6703795949</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:4">
+      <x:c r="A138" s="1">
+        <x:v>45815.6703802199</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D138" s="2" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:4">
+      <x:c r="A139" s="1">
+        <x:v>45815.6747401505</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:4">
+      <x:c r="A140" s="1">
+        <x:v>45815.6747406019</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D140" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:4">
+      <x:c r="A141" s="1">
+        <x:v>45815.6806210185</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:4">
+      <x:c r="A142" s="1">
+        <x:v>45815.6806212037</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D142" s="2" t="s">
+        <x:v>81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:4">
+      <x:c r="A143" s="1">
+        <x:v>45815.6833676042</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:4">
+      <x:c r="A144" s="1">
+        <x:v>45815.6833680787</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D144" s="2" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:4">
+      <x:c r="A145" s="1">
+        <x:v>45815.6854657176</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:4">
+      <x:c r="A146" s="1">
+        <x:v>45815.6854662731</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D146" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:4">
+      <x:c r="A147" s="1">
+        <x:v>45815.6862563889</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:4">
+      <x:c r="A148" s="1">
+        <x:v>45815.6862575231</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D148" s="2" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:4">
+      <x:c r="A149" s="1">
+        <x:v>45815.6878410532</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:4">
+      <x:c r="A150" s="1">
+        <x:v>45815.6878415046</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D150" s="2" t="s">
+        <x:v>85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:4">
+      <x:c r="A151" s="1">
+        <x:v>45815.6885357639</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:4">
+      <x:c r="A152" s="1">
+        <x:v>45815.6885363773</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D152" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:4">
+      <x:c r="A153" s="1">
+        <x:v>45815.6909991319</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:4">
+      <x:c r="A154" s="1">
+        <x:v>45815.6909997801</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D154" s="2" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:4">
+      <x:c r="A155" s="1">
+        <x:v>45815.6955497454</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:4">
+      <x:c r="A156" s="1">
+        <x:v>45815.6955502894</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D156" s="2" t="s">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:4">
+      <x:c r="A157" s="1">
+        <x:v>45815.6968929167</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:4">
+      <x:c r="A158" s="1">
+        <x:v>45815.6968934375</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D158" s="2" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:4">
+      <x:c r="A159" s="1">
+        <x:v>45815.6979318171</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:4">
+      <x:c r="A160" s="1">
+        <x:v>45815.6979322801</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D160" s="2" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:4">
+      <x:c r="A161" s="1">
+        <x:v>45815.6996943287</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:4">
+      <x:c r="A162" s="1">
+        <x:v>45815.6996949074</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D162" s="2" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:4">
+      <x:c r="A163" s="1">
+        <x:v>45815.7009476736</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:4">
+      <x:c r="A164" s="1">
+        <x:v>45815.7009481944</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D164" s="2" t="s">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:4">
+      <x:c r="A165" s="1">
+        <x:v>45815.7033692593</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:4">
+      <x:c r="A166" s="1">
+        <x:v>45815.7033697338</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D166" s="2" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:4">
+      <x:c r="A167" s="1">
+        <x:v>45815.7213020255</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:4">
+      <x:c r="A168" s="1">
+        <x:v>45815.7213025231</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D168" s="2" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:4">
+      <x:c r="A169" s="1">
+        <x:v>45815.7214389236</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:4">
+      <x:c r="A170" s="1">
+        <x:v>45815.7214389236</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:4">
+      <x:c r="A171" s="1">
+        <x:v>45815.7214389352</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:4">
+      <x:c r="A172" s="1">
+        <x:v>45815.7214389352</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:4">
+      <x:c r="A173" s="1">
+        <x:v>45815.7228266551</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:4">
+      <x:c r="A174" s="1">
+        <x:v>45815.7228271991</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D174" s="2" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:4">
+      <x:c r="A175" s="1">
+        <x:v>45815.7228899537</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:4">
+      <x:c r="A176" s="1">
+        <x:v>45815.7228899769</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:4">
+      <x:c r="A177" s="1">
+        <x:v>45815.7229176273</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:4">
+      <x:c r="A178" s="1">
+        <x:v>45815.7229176273</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:4">
+      <x:c r="A179" s="1">
+        <x:v>45815.7230407176</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:4">
+      <x:c r="A180" s="1">
+        <x:v>45815.7230407176</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:4">
+      <x:c r="A181" s="1">
+        <x:v>45815.7239173264</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:4">
+      <x:c r="A182" s="1">
+        <x:v>45815.7252501389</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:4">
+      <x:c r="A183" s="1">
+        <x:v>45815.7252507292</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D183" s="2" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:4">
+      <x:c r="A184" s="1">
+        <x:v>45815.7272975347</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:4">
+      <x:c r="A185" s="1">
+        <x:v>45815.7272983796</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D185" s="2" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:4">
+      <x:c r="A186" s="1">
+        <x:v>45815.7859162963</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:4">
+      <x:c r="A187" s="1">
+        <x:v>45815.7859168403</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D187" s="2" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:4">
+      <x:c r="A188" s="1">
+        <x:v>45815.7862637616</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:4">
+      <x:c r="A189" s="1">
+        <x:v>45815.7862637616</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:4">
+      <x:c r="A190" s="1">
+        <x:v>45815.7862637616</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:4">
+      <x:c r="A191" s="1">
+        <x:v>45815.7862637616</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:4">
+      <x:c r="A192" s="1">
+        <x:v>45815.8579779861</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:4">
+      <x:c r="A193" s="1">
+        <x:v>45815.8579789236</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D193" s="2" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:4">
+      <x:c r="A194" s="1">
+        <x:v>45815.8595430671</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:4">
+      <x:c r="A195" s="1">
+        <x:v>45815.8595432639</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D195" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:4">
+      <x:c r="A196" s="1">
+        <x:v>45815.8694790162</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:4">
+      <x:c r="A197" s="1">
+        <x:v>45815.8694795486</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D197" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:4">
+      <x:c r="A198" s="1">
+        <x:v>45815.8698747338</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:4">
+      <x:c r="A199" s="1">
+        <x:v>45815.8698747454</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:4">
+      <x:c r="A200" s="1">
+        <x:v>45815.8698747454</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:4">
+      <x:c r="A201" s="1">
+        <x:v>45815.8698747454</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:4">
+      <x:c r="A202" s="1">
+        <x:v>45815.8732847569</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C202" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D202" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:4">
+      <x:c r="A203" s="1">
+        <x:v>45815.8732853472</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C203" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D203" s="2" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:4">
+      <x:c r="A204" s="1">
+        <x:v>45815.8734802083</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C204" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D204" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:4">
+      <x:c r="A205" s="1">
+        <x:v>45815.8734802083</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C205" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D205" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:4">
+      <x:c r="A206" s="1">
+        <x:v>45815.8734802083</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C206" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D206" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:4">
+      <x:c r="A207" s="1">
+        <x:v>45815.8734802083</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C207" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D207" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:4">
+      <x:c r="A208" s="1">
+        <x:v>45817.3883152315</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C208" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D208" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:4">
+      <x:c r="A209" s="1">
+        <x:v>45817.3883155787</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C209" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D209" s="2" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:4">
+      <x:c r="A210" s="1">
+        <x:v>45817.3886493981</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C210" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D210" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:4">
+      <x:c r="A211" s="1">
+        <x:v>45817.3886497569</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C211" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D211" s="2" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:4">
+      <x:c r="A212" s="1">
+        <x:v>45817.3889217824</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C212" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D212" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:4">
+      <x:c r="A213" s="1">
+        <x:v>45817.3897213773</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C213" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D213" s="2" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:4">
+      <x:c r="A214" s="1">
+        <x:v>45817.4221195718</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C214" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D214" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:4">
+      <x:c r="A215" s="1">
+        <x:v>45817.4221198032</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C215" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D215" s="2" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:4">
+      <x:c r="A216" s="1">
+        <x:v>45817.4223817245</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C216" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D216" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:4">
+      <x:c r="A217" s="1">
+        <x:v>45817.4354826505</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C217" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D217" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:4">
+      <x:c r="A218" s="1">
+        <x:v>45817.4354829514</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C218" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D218" s="2" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:4">
+      <x:c r="A219" s="1">
+        <x:v>45817.4355819097</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C219" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D219" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:4">
+      <x:c r="A220" s="1">
+        <x:v>45817.4366669676</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C220" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D220" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:4">
+      <x:c r="A221" s="1">
+        <x:v>45817.4366673495</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C221" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D221" s="2" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:4">
+      <x:c r="A222" s="1">
+        <x:v>45817.4378078356</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C222" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D222" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:4">
+      <x:c r="A223" s="1">
+        <x:v>45817.4378084954</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C223" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D223" s="2" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:4">
+      <x:c r="A224" s="1">
+        <x:v>45817.4401240741</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C224" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D224" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:4">
+      <x:c r="A225" s="1">
+        <x:v>45817.4401243171</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C225" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D225" s="2" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:4">
+      <x:c r="A226" s="1">
+        <x:v>45817.4414899769</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C226" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D226" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:4">
+      <x:c r="A227" s="1">
+        <x:v>45817.4414903356</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C227" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D227" s="2" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:4">
+      <x:c r="A228" s="1">
+        <x:v>45817.4416133681</x:v>
+      </x:c>
+      <x:c r="B228" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C228" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D228" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:4">
+      <x:c r="A229" s="1">
+        <x:v>45817.4416848611</x:v>
+      </x:c>
+      <x:c r="B229" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C229" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D229" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:4">
+      <x:c r="A230" s="1">
+        <x:v>45817.4417321181</x:v>
+      </x:c>
+      <x:c r="B230" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C230" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D230" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:4">
+      <x:c r="A231" s="1">
+        <x:v>45817.442450706</x:v>
+      </x:c>
+      <x:c r="B231" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C231" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D231" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:4">
+      <x:c r="A232" s="1">
+        <x:v>45817.4507747801</x:v>
+      </x:c>
+      <x:c r="B232" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C232" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D232" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:4">
+      <x:c r="A233" s="1">
+        <x:v>45817.4507754514</x:v>
+      </x:c>
+      <x:c r="B233" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C233" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D233" s="2" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:4">
+      <x:c r="A234" s="1">
+        <x:v>45817.4509172454</x:v>
+      </x:c>
+      <x:c r="B234" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C234" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D234" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:4">
+      <x:c r="A235" s="1">
+        <x:v>45817.4509569444</x:v>
+      </x:c>
+      <x:c r="B235" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C235" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D235" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:4">
+      <x:c r="A236" s="1">
+        <x:v>45817.450964213</x:v>
+      </x:c>
+      <x:c r="B236" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C236" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D236" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:4">
+      <x:c r="A237" s="1">
+        <x:v>45817.4510081366</x:v>
+      </x:c>
+      <x:c r="B237" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C237" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D237" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:4">
+      <x:c r="A238" s="1">
+        <x:v>45817.4510081366</x:v>
+      </x:c>
+      <x:c r="B238" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C238" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D238" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:4">
+      <x:c r="A239" s="1">
+        <x:v>45817.4648137616</x:v>
+      </x:c>
+      <x:c r="B239" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C239" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D239" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:4">
+      <x:c r="A240" s="1">
+        <x:v>45817.4648139815</x:v>
+      </x:c>
+      <x:c r="B240" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C240" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D240" s="2" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:4">
+      <x:c r="A241" s="1">
+        <x:v>45817.4704310301</x:v>
+      </x:c>
+      <x:c r="B241" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C241" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D241" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:4">
+      <x:c r="A242" s="1">
+        <x:v>45817.4704312269</x:v>
+      </x:c>
+      <x:c r="B242" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C242" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D242" s="2" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:4">
+      <x:c r="A243" s="1">
+        <x:v>45817.4799321065</x:v>
+      </x:c>
+      <x:c r="B243" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C243" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D243" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:4">
+      <x:c r="A244" s="1">
+        <x:v>45817.4799323264</x:v>
+      </x:c>
+      <x:c r="B244" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C244" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D244" s="2" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:4">
+      <x:c r="A245" s="1">
+        <x:v>45817.4799330556</x:v>
+      </x:c>
+      <x:c r="B245" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C245" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D245" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:4">
+      <x:c r="A246" s="1">
+        <x:v>45817.4799333102</x:v>
+      </x:c>
+      <x:c r="B246" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C246" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D246" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:4">
+      <x:c r="A247" s="1">
+        <x:v>45817.4799335417</x:v>
+      </x:c>
+      <x:c r="B247" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C247" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D247" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:4">
+      <x:c r="A248" s="1">
+        <x:v>45817.4833702083</x:v>
+      </x:c>
+      <x:c r="B248" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C248" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D248" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:4">
+      <x:c r="A249" s="1">
+        <x:v>45817.4833704051</x:v>
+      </x:c>
+      <x:c r="B249" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C249" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D249" s="2" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:4">
+      <x:c r="A250" s="1">
+        <x:v>45817.48350125</x:v>
+      </x:c>
+      <x:c r="B250" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C250" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D250" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:4">
+      <x:c r="A251" s="1">
+        <x:v>45817.4835014931</x:v>
+      </x:c>
+      <x:c r="B251" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C251" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D251" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:4">
+      <x:c r="A252" s="1">
+        <x:v>45817.4835014931</x:v>
+      </x:c>
+      <x:c r="B252" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C252" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D252" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:4">
+      <x:c r="A253" s="1">
+        <x:v>45817.4835014931</x:v>
+      </x:c>
+      <x:c r="B253" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C253" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D253" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:4">
+      <x:c r="A254" s="1">
+        <x:v>45817.4841715393</x:v>
+      </x:c>
+      <x:c r="B254" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C254" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D254" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:4">
+      <x:c r="A255" s="1">
+        <x:v>45817.4862975</x:v>
+      </x:c>
+      <x:c r="B255" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C255" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D255" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:4">
+      <x:c r="A256" s="1">
+        <x:v>45817.4862976852</x:v>
+      </x:c>
+      <x:c r="B256" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C256" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D256" s="2" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:4">
+      <x:c r="A257" s="1">
+        <x:v>45817.5136280093</x:v>
+      </x:c>
+      <x:c r="B257" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C257" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D257" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:4">
+      <x:c r="A258" s="1">
+        <x:v>45817.5136287269</x:v>
+      </x:c>
+      <x:c r="B258" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C258" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D258" s="2" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:4">
+      <x:c r="A259" s="1">
+        <x:v>45817.5305062731</x:v>
+      </x:c>
+      <x:c r="B259" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C259" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D259" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:4">
+      <x:c r="A260" s="1">
+        <x:v>45817.530506875</x:v>
+      </x:c>
+      <x:c r="B260" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C260" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D260" s="2" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:4">
+      <x:c r="A261" s="1">
+        <x:v>45817.5307448727</x:v>
+      </x:c>
+      <x:c r="B261" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C261" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D261" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:4">
+      <x:c r="A262" s="1">
+        <x:v>45817.5344437616</x:v>
+      </x:c>
+      <x:c r="B262" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C262" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D262" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:4">
+      <x:c r="A263" s="1">
+        <x:v>45817.5344439699</x:v>
+      </x:c>
+      <x:c r="B263" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C263" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D263" s="2" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
+++ b/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
@@ -654,6 +654,331 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-06-09 12:49:35]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 21:53:15]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]800219,[Msg]Site0温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]801219,[Msg]Site1温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]802219,[Msg]Site2温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]803219,[Msg]Site3温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]804219,[Msg]Site4温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]805219,[Msg]Site5温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]806219,[Msg]Site6温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]807219,[Msg]Site7温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]808219,[Msg]Site8温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]809219,[Msg]Site9温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]810219,[Msg]Site10温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]811219,[Msg]Site11温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]812219,[Msg]Site12温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]813219,[Msg]Site13温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]814219,[Msg]Site14温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code]815219,[Msg]加热盘温度异常!</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 21:54:56]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 21:55:50]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-09 22:29:56]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 09:39:42]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 09:47:52]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 09:51:24]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 10:14:52]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code][Msg]后梭车(梭车2)Dut01有IC遗留</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code][Msg]后梭车(梭车2)Dut06有IC遗留</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code][Msg]前梭车(梭车1)Dut03有IC遗留</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[Code][Msg]前梭车(梭车1)Dut08有IC遗留</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 14:47:57]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 14:50:34]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 15:58:15]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_22_18_02 where 名称='auto2'，错误信息：对象名 'o_ZRS240929001A_20250606_22_18_02' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_22_18_02 where 名称='fix1'，错误信息：对象名 'o_ZRS240929001A_20250606_22_18_02' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_22_18_02 where 名称='fix2'，错误信息：对象名 'o_ZRS240929001A_20250606_22_18_02' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_22_18_02 where 名称='fix3'，错误信息：对象名 'o_ZRS240929001A_20250606_22_18_02' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_23_27_58 where 名称='auto2'，错误信息：对象名 'o_ZRS240929001A_20250606_23_27_58' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_23_27_58 where 名称='fix1'，错误信息：对象名 'o_ZRS240929001A_20250606_23_27_58' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_23_27_58 where 名称='fix2'，错误信息：对象名 'o_ZRS240929001A_20250606_23_27_58' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250606_23_27_58 where 名称='fix3'，错误信息：对象名 'o_ZRS240929001A_20250606_23_27_58' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250607_10_23_42 where 名称='auto2'，错误信息：对象名 'o_ZRS240929001A_20250607_10_23_42' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250607_10_23_42 where 名称='fix1'，错误信息：对象名 'o_ZRS240929001A_20250607_10_23_42' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250607_10_23_42 where 名称='fix2'，错误信息：对象名 'o_ZRS240929001A_20250607_10_23_42' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select count(*) from o_ZRS240929001A_20250607_10_23_42 where 名称='fix3'，错误信息：对象名 'o_ZRS240929001A_20250607_10_23_42' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select * from f_ZRS240929001A_20250607_10_23_42  order by 获取MAP时间，错误信息：对象名 'f_ZRS240929001A_20250607_10_23_42' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select * from f_ZRS240929001A_20250606_22_18_02  order by 获取MAP时间，错误信息：对象名 'f_ZRS240929001A_20250606_22_18_02' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select * from f_ZRS240929001A_20250606_23_27_58  order by 获取MAP时间，错误信息：对象名 'f_ZRS240929001A_20250606_23_27_58' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：SELECT * FROM dut_ZRS240929001A_20250606_22_18_02，错误信息：对象名 'dut_ZRS240929001A_20250606_22_18_02' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：SELECT * FROM dut_ZRS240929001A_20250606_23_27_58，错误信息：对象名 'dut_ZRS240929001A_20250606_23_27_58' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@START_TEST 00 00000000+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 16:03:20]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 16:09:13]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 16:25:50]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称-[6x12_UFS]-加热盘名称-[6x12_UFS]-[IC加热时间]120-&gt;121:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称-[6x12_UFS]-加热盘名称-[6x12_UFS]-[达温后延时]120-&gt;121:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称-[6x12_UFS]-加热盘名称-[6x12_UFS]-[IC加热时间]121-&gt;120:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称-[6x12_UFS]-加热盘名称-[6x12_UFS]-[达温后延时]121-&gt;120:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 17:12:00]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 19:01:49]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 19:03:42]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 19:12:30]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 19:37:07]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 19:52:26]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 19:55:55]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>读取当前档案信息失败!无点位微调默认信息</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 20:02:02]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案切换[8X19_UFS_OnLine]-&gt;[默认]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案切换[默认]-&gt;[8X19_UFS_OnLine]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 20:09:51]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 20:13:54]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 20:19:52]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案切换[8X19_UFS_OnLine]-&gt;[8X19_eMMC_OnLine]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 20:21:38]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案切换[8X19_eMMC_OnLine]-&gt;[8X19_UFS_OnLine]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 20:52:59]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 21:54:35]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：insert into TesterIFParam(测试机名称,auto1,auto2,fix1,fix2,fix3)values('9875','01','02,20A,OTH','03;;','04;;','05;;')，错误信息：SQL logic error
+table TesterIFParam has no column named auto1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 21:58:13]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-10 22:10:45]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
@@ -4703,6 +5028,2274 @@
         <x:v>134</x:v>
       </x:c>
     </x:row>
+    <x:row r="264" spans="1:4">
+      <x:c r="A264" s="1">
+        <x:v>45817.9119815278</x:v>
+      </x:c>
+      <x:c r="B264" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C264" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D264" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:4">
+      <x:c r="A265" s="1">
+        <x:v>45817.9119817245</x:v>
+      </x:c>
+      <x:c r="B265" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C265" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D265" s="2" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:4">
+      <x:c r="A266" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B266" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C266" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D266" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:4">
+      <x:c r="A267" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B267" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C267" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D267" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:4">
+      <x:c r="A268" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B268" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C268" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D268" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:4">
+      <x:c r="A269" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B269" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C269" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D269" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:4">
+      <x:c r="A270" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B270" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C270" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D270" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:4">
+      <x:c r="A271" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B271" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C271" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D271" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:4">
+      <x:c r="A272" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B272" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C272" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D272" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:4">
+      <x:c r="A273" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B273" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C273" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D273" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:4">
+      <x:c r="A274" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B274" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C274" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D274" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:4">
+      <x:c r="A275" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B275" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C275" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D275" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:4">
+      <x:c r="A276" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B276" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C276" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D276" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:4">
+      <x:c r="A277" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B277" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C277" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D277" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:4">
+      <x:c r="A278" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B278" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C278" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D278" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:4">
+      <x:c r="A279" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B279" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C279" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D279" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:4">
+      <x:c r="A280" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B280" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C280" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D280" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:4">
+      <x:c r="A281" s="1">
+        <x:v>45817.9121177894</x:v>
+      </x:c>
+      <x:c r="B281" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C281" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D281" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:4">
+      <x:c r="A282" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B282" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C282" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D282" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:4">
+      <x:c r="A283" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B283" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C283" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D283" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:4">
+      <x:c r="A284" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B284" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C284" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D284" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:4">
+      <x:c r="A285" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B285" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C285" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D285" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:4">
+      <x:c r="A286" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B286" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C286" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D286" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:4">
+      <x:c r="A287" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B287" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C287" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D287" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:4">
+      <x:c r="A288" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B288" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C288" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D288" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:4">
+      <x:c r="A289" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B289" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C289" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D289" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:4">
+      <x:c r="A290" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B290" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C290" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D290" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:4">
+      <x:c r="A291" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B291" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C291" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D291" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:4">
+      <x:c r="A292" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B292" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C292" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D292" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:4">
+      <x:c r="A293" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B293" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C293" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D293" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:4">
+      <x:c r="A294" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B294" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C294" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D294" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:4">
+      <x:c r="A295" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B295" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C295" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D295" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:4">
+      <x:c r="A296" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B296" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C296" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D296" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:4">
+      <x:c r="A297" s="1">
+        <x:v>45817.9126160069</x:v>
+      </x:c>
+      <x:c r="B297" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C297" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D297" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:4">
+      <x:c r="A298" s="1">
+        <x:v>45817.9131553009</x:v>
+      </x:c>
+      <x:c r="B298" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C298" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D298" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:4">
+      <x:c r="A299" s="1">
+        <x:v>45817.9131560301</x:v>
+      </x:c>
+      <x:c r="B299" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C299" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D299" s="2" t="s">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:4">
+      <x:c r="A300" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B300" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C300" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D300" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:4">
+      <x:c r="A301" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B301" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C301" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D301" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:4">
+      <x:c r="A302" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D302" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:4">
+      <x:c r="A303" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D303" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:4">
+      <x:c r="A304" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D304" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:4">
+      <x:c r="A305" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B305" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C305" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D305" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:4">
+      <x:c r="A306" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B306" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C306" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D306" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:4">
+      <x:c r="A307" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B307" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C307" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D307" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:4">
+      <x:c r="A308" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B308" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C308" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D308" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:4">
+      <x:c r="A309" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B309" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C309" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D309" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:4">
+      <x:c r="A310" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B310" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C310" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D310" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:4">
+      <x:c r="A311" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B311" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C311" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D311" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:4">
+      <x:c r="A312" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B312" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C312" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D312" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:4">
+      <x:c r="A313" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B313" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C313" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D313" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:4">
+      <x:c r="A314" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B314" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C314" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D314" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:4">
+      <x:c r="A315" s="1">
+        <x:v>45817.9132215278</x:v>
+      </x:c>
+      <x:c r="B315" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C315" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D315" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:4">
+      <x:c r="A316" s="1">
+        <x:v>45817.91377875</x:v>
+      </x:c>
+      <x:c r="B316" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C316" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D316" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:4">
+      <x:c r="A317" s="1">
+        <x:v>45817.9137789352</x:v>
+      </x:c>
+      <x:c r="B317" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C317" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D317" s="2" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:4">
+      <x:c r="A318" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B318" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C318" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D318" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:4">
+      <x:c r="A319" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B319" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C319" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D319" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:4">
+      <x:c r="A320" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B320" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C320" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D320" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:4">
+      <x:c r="A321" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B321" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C321" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D321" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:4">
+      <x:c r="A322" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B322" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C322" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D322" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:4">
+      <x:c r="A323" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B323" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C323" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D323" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:4">
+      <x:c r="A324" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B324" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C324" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D324" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:4">
+      <x:c r="A325" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B325" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C325" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D325" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:4">
+      <x:c r="A326" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B326" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C326" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D326" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:4">
+      <x:c r="A327" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B327" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C327" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D327" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:4">
+      <x:c r="A328" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B328" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C328" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D328" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:4">
+      <x:c r="A329" s="1">
+        <x:v>45817.9138298032</x:v>
+      </x:c>
+      <x:c r="B329" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C329" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D329" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:4">
+      <x:c r="A330" s="1">
+        <x:v>45817.9138298148</x:v>
+      </x:c>
+      <x:c r="B330" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C330" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D330" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:4">
+      <x:c r="A331" s="1">
+        <x:v>45817.9138298148</x:v>
+      </x:c>
+      <x:c r="B331" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C331" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D331" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:4">
+      <x:c r="A332" s="1">
+        <x:v>45817.9138298148</x:v>
+      </x:c>
+      <x:c r="B332" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C332" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D332" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:4">
+      <x:c r="A333" s="1">
+        <x:v>45817.9138298148</x:v>
+      </x:c>
+      <x:c r="B333" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C333" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D333" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:4">
+      <x:c r="A334" s="1">
+        <x:v>45817.937456088</x:v>
+      </x:c>
+      <x:c r="B334" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C334" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D334" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:4">
+      <x:c r="A335" s="1">
+        <x:v>45817.9374564815</x:v>
+      </x:c>
+      <x:c r="B335" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C335" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D335" s="2" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:4">
+      <x:c r="A336" s="1">
+        <x:v>45818.4025796181</x:v>
+      </x:c>
+      <x:c r="B336" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C336" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D336" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:4">
+      <x:c r="A337" s="1">
+        <x:v>45818.4025799653</x:v>
+      </x:c>
+      <x:c r="B337" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C337" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D337" s="2" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" spans="1:4">
+      <x:c r="A338" s="1">
+        <x:v>45818.4082423727</x:v>
+      </x:c>
+      <x:c r="B338" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C338" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D338" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" spans="1:4">
+      <x:c r="A339" s="1">
+        <x:v>45818.4082425347</x:v>
+      </x:c>
+      <x:c r="B339" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C339" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D339" s="2" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" spans="1:4">
+      <x:c r="A340" s="1">
+        <x:v>45818.4107027431</x:v>
+      </x:c>
+      <x:c r="B340" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C340" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D340" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" spans="1:4">
+      <x:c r="A341" s="1">
+        <x:v>45818.4107029167</x:v>
+      </x:c>
+      <x:c r="B341" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C341" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D341" s="2" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" spans="1:4">
+      <x:c r="A342" s="1">
+        <x:v>45818.4269922685</x:v>
+      </x:c>
+      <x:c r="B342" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C342" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D342" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" spans="1:4">
+      <x:c r="A343" s="1">
+        <x:v>45818.4269925</x:v>
+      </x:c>
+      <x:c r="B343" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C343" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D343" s="2" t="s">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" spans="1:4">
+      <x:c r="A344" s="1">
+        <x:v>45818.427646713</x:v>
+      </x:c>
+      <x:c r="B344" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C344" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D344" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" spans="1:4">
+      <x:c r="A345" s="1">
+        <x:v>45818.427646713</x:v>
+      </x:c>
+      <x:c r="B345" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C345" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D345" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" spans="1:4">
+      <x:c r="A346" s="1">
+        <x:v>45818.427646713</x:v>
+      </x:c>
+      <x:c r="B346" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C346" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D346" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" spans="1:4">
+      <x:c r="A347" s="1">
+        <x:v>45818.427646713</x:v>
+      </x:c>
+      <x:c r="B347" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C347" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D347" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" spans="1:4">
+      <x:c r="A348" s="1">
+        <x:v>45818.6166365972</x:v>
+      </x:c>
+      <x:c r="B348" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C348" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D348" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" spans="1:4">
+      <x:c r="A349" s="1">
+        <x:v>45818.6166367708</x:v>
+      </x:c>
+      <x:c r="B349" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C349" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D349" s="2" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" spans="1:4">
+      <x:c r="A350" s="1">
+        <x:v>45818.6184589005</x:v>
+      </x:c>
+      <x:c r="B350" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C350" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D350" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" spans="1:4">
+      <x:c r="A351" s="1">
+        <x:v>45818.6184590857</x:v>
+      </x:c>
+      <x:c r="B351" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C351" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D351" s="2" t="s">
+        <x:v>164</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" spans="1:4">
+      <x:c r="A352" s="1">
+        <x:v>45818.6654594097</x:v>
+      </x:c>
+      <x:c r="B352" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C352" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D352" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" spans="1:4">
+      <x:c r="A353" s="1">
+        <x:v>45818.6654597222</x:v>
+      </x:c>
+      <x:c r="B353" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C353" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D353" s="2" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" spans="1:4">
+      <x:c r="A354" s="1">
+        <x:v>45818.6662966898</x:v>
+      </x:c>
+      <x:c r="B354" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C354" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D354" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" spans="1:4">
+      <x:c r="A355" s="1">
+        <x:v>45818.666297419</x:v>
+      </x:c>
+      <x:c r="B355" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C355" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D355" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" spans="1:4">
+      <x:c r="A356" s="1">
+        <x:v>45818.666297662</x:v>
+      </x:c>
+      <x:c r="B356" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C356" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D356" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" spans="1:4">
+      <x:c r="A357" s="1">
+        <x:v>45818.6662978935</x:v>
+      </x:c>
+      <x:c r="B357" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C357" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D357" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" spans="1:4">
+      <x:c r="A358" s="1">
+        <x:v>45818.6663112037</x:v>
+      </x:c>
+      <x:c r="B358" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C358" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D358" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" spans="1:4">
+      <x:c r="A359" s="1">
+        <x:v>45818.6663114352</x:v>
+      </x:c>
+      <x:c r="B359" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C359" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D359" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" spans="1:4">
+      <x:c r="A360" s="1">
+        <x:v>45818.6663116551</x:v>
+      </x:c>
+      <x:c r="B360" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C360" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D360" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" spans="1:4">
+      <x:c r="A361" s="1">
+        <x:v>45818.6663118981</x:v>
+      </x:c>
+      <x:c r="B361" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C361" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D361" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" spans="1:4">
+      <x:c r="A362" s="1">
+        <x:v>45818.6663191088</x:v>
+      </x:c>
+      <x:c r="B362" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C362" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D362" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" spans="1:4">
+      <x:c r="A363" s="1">
+        <x:v>45818.6663193403</x:v>
+      </x:c>
+      <x:c r="B363" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C363" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D363" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" spans="1:4">
+      <x:c r="A364" s="1">
+        <x:v>45818.6663196065</x:v>
+      </x:c>
+      <x:c r="B364" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C364" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D364" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" spans="1:4">
+      <x:c r="A365" s="1">
+        <x:v>45818.6663199074</x:v>
+      </x:c>
+      <x:c r="B365" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C365" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D365" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" spans="1:4">
+      <x:c r="A366" s="1">
+        <x:v>45818.666652338</x:v>
+      </x:c>
+      <x:c r="B366" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C366" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D366" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" spans="1:4">
+      <x:c r="A367" s="1">
+        <x:v>45818.6666527315</x:v>
+      </x:c>
+      <x:c r="B367" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C367" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D367" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" spans="1:4">
+      <x:c r="A368" s="1">
+        <x:v>45818.666652963</x:v>
+      </x:c>
+      <x:c r="B368" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C368" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D368" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" spans="1:4">
+      <x:c r="A369" s="1">
+        <x:v>45818.6666531944</x:v>
+      </x:c>
+      <x:c r="B369" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C369" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D369" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" spans="1:4">
+      <x:c r="A370" s="1">
+        <x:v>45818.6666642477</x:v>
+      </x:c>
+      <x:c r="B370" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C370" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D370" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" spans="1:4">
+      <x:c r="A371" s="1">
+        <x:v>45818.6666760301</x:v>
+      </x:c>
+      <x:c r="B371" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C371" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D371" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" spans="1:4">
+      <x:c r="A372" s="1">
+        <x:v>45818.6668370023</x:v>
+      </x:c>
+      <x:c r="B372" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C372" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D372" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" spans="1:4">
+      <x:c r="A373" s="1">
+        <x:v>45818.6668417824</x:v>
+      </x:c>
+      <x:c r="B373" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C373" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D373" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" spans="1:4">
+      <x:c r="A374" s="1">
+        <x:v>45818.6668491782</x:v>
+      </x:c>
+      <x:c r="B374" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C374" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D374" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" spans="1:4">
+      <x:c r="A375" s="1">
+        <x:v>45818.6678041667</x:v>
+      </x:c>
+      <x:c r="B375" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C375" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D375" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" spans="1:4">
+      <x:c r="A376" s="1">
+        <x:v>45818.6678512847</x:v>
+      </x:c>
+      <x:c r="B376" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C376" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D376" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" spans="1:4">
+      <x:c r="A377" s="1">
+        <x:v>45818.6680667014</x:v>
+      </x:c>
+      <x:c r="B377" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C377" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D377" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" spans="1:4">
+      <x:c r="A378" s="1">
+        <x:v>45818.6689837616</x:v>
+      </x:c>
+      <x:c r="B378" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C378" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D378" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" spans="1:4">
+      <x:c r="A379" s="1">
+        <x:v>45818.6689843171</x:v>
+      </x:c>
+      <x:c r="B379" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C379" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D379" s="2" t="s">
+        <x:v>184</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" spans="1:4">
+      <x:c r="A380" s="1">
+        <x:v>45818.6730715278</x:v>
+      </x:c>
+      <x:c r="B380" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C380" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D380" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" spans="1:4">
+      <x:c r="A381" s="1">
+        <x:v>45818.6730721528</x:v>
+      </x:c>
+      <x:c r="B381" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C381" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D381" s="2" t="s">
+        <x:v>185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" spans="1:4">
+      <x:c r="A382" s="1">
+        <x:v>45818.6846133796</x:v>
+      </x:c>
+      <x:c r="B382" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C382" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D382" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" spans="1:4">
+      <x:c r="A383" s="1">
+        <x:v>45818.6846135417</x:v>
+      </x:c>
+      <x:c r="B383" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C383" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D383" s="2" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" spans="1:4">
+      <x:c r="A384" s="1">
+        <x:v>45818.6851963426</x:v>
+      </x:c>
+      <x:c r="B384" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C384" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D384" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" spans="1:4">
+      <x:c r="A385" s="1">
+        <x:v>45818.6851963889</x:v>
+      </x:c>
+      <x:c r="B385" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C385" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D385" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" spans="1:4">
+      <x:c r="A386" s="1">
+        <x:v>45818.6874755208</x:v>
+      </x:c>
+      <x:c r="B386" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C386" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D386" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" spans="1:4">
+      <x:c r="A387" s="1">
+        <x:v>45818.6874755556</x:v>
+      </x:c>
+      <x:c r="B387" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C387" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D387" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" spans="1:4">
+      <x:c r="A388" s="1">
+        <x:v>45818.7166690046</x:v>
+      </x:c>
+      <x:c r="B388" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C388" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D388" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" spans="1:4">
+      <x:c r="A389" s="1">
+        <x:v>45818.7166691667</x:v>
+      </x:c>
+      <x:c r="B389" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C389" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D389" s="2" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" spans="1:4">
+      <x:c r="A390" s="1">
+        <x:v>45818.7929335764</x:v>
+      </x:c>
+      <x:c r="B390" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C390" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D390" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" spans="1:4">
+      <x:c r="A391" s="1">
+        <x:v>45818.79293375</x:v>
+      </x:c>
+      <x:c r="B391" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C391" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D391" s="2" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" spans="1:4">
+      <x:c r="A392" s="1">
+        <x:v>45818.7942472801</x:v>
+      </x:c>
+      <x:c r="B392" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C392" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D392" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" spans="1:4">
+      <x:c r="A393" s="1">
+        <x:v>45818.7942476157</x:v>
+      </x:c>
+      <x:c r="B393" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C393" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D393" s="2" t="s">
+        <x:v>193</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" spans="1:4">
+      <x:c r="A394" s="1">
+        <x:v>45818.8003523032</x:v>
+      </x:c>
+      <x:c r="B394" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C394" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D394" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" spans="1:4">
+      <x:c r="A395" s="1">
+        <x:v>45818.8003524769</x:v>
+      </x:c>
+      <x:c r="B395" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C395" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D395" s="2" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" spans="1:4">
+      <x:c r="A396" s="1">
+        <x:v>45818.8174514352</x:v>
+      </x:c>
+      <x:c r="B396" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C396" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D396" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" spans="1:4">
+      <x:c r="A397" s="1">
+        <x:v>45818.8174516088</x:v>
+      </x:c>
+      <x:c r="B397" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C397" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D397" s="2" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" spans="1:4">
+      <x:c r="A398" s="1">
+        <x:v>45818.8280870602</x:v>
+      </x:c>
+      <x:c r="B398" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C398" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D398" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" spans="1:4">
+      <x:c r="A399" s="1">
+        <x:v>45818.8280872222</x:v>
+      </x:c>
+      <x:c r="B399" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C399" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D399" s="2" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" spans="1:4">
+      <x:c r="A400" s="1">
+        <x:v>45818.8305025347</x:v>
+      </x:c>
+      <x:c r="B400" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C400" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D400" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" spans="1:4">
+      <x:c r="A401" s="1">
+        <x:v>45818.8305027199</x:v>
+      </x:c>
+      <x:c r="B401" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C401" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D401" s="2" t="s">
+        <x:v>197</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" spans="1:4">
+      <x:c r="A402" s="1">
+        <x:v>45818.8310021991</x:v>
+      </x:c>
+      <x:c r="B402" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C402" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D402" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" spans="1:4">
+      <x:c r="A403" s="1">
+        <x:v>45818.8347460069</x:v>
+      </x:c>
+      <x:c r="B403" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C403" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D403" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" spans="1:4">
+      <x:c r="A404" s="1">
+        <x:v>45818.8347461806</x:v>
+      </x:c>
+      <x:c r="B404" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C404" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D404" s="2" t="s">
+        <x:v>199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" spans="1:4">
+      <x:c r="A405" s="1">
+        <x:v>45818.8350700926</x:v>
+      </x:c>
+      <x:c r="B405" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C405" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D405" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" spans="1:4">
+      <x:c r="A406" s="1">
+        <x:v>45818.8353147454</x:v>
+      </x:c>
+      <x:c r="B406" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C406" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D406" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:4">
+      <x:c r="A407" s="1">
+        <x:v>45818.8401736806</x:v>
+      </x:c>
+      <x:c r="B407" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C407" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D407" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:4">
+      <x:c r="A408" s="1">
+        <x:v>45818.8401738542</x:v>
+      </x:c>
+      <x:c r="B408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C408" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D408" s="2" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:4">
+      <x:c r="A409" s="1">
+        <x:v>45818.8429869213</x:v>
+      </x:c>
+      <x:c r="B409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C409" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D409" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:4">
+      <x:c r="A410" s="1">
+        <x:v>45818.8429871528</x:v>
+      </x:c>
+      <x:c r="B410" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C410" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D410" s="2" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:4">
+      <x:c r="A411" s="1">
+        <x:v>45818.8471390857</x:v>
+      </x:c>
+      <x:c r="B411" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C411" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D411" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:4">
+      <x:c r="A412" s="1">
+        <x:v>45818.8471392708</x:v>
+      </x:c>
+      <x:c r="B412" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C412" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D412" s="2" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:4">
+      <x:c r="A413" s="1">
+        <x:v>45818.8475206597</x:v>
+      </x:c>
+      <x:c r="B413" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C413" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D413" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:4">
+      <x:c r="A414" s="1">
+        <x:v>45818.84835875</x:v>
+      </x:c>
+      <x:c r="B414" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C414" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D414" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:4">
+      <x:c r="A415" s="1">
+        <x:v>45818.8483589699</x:v>
+      </x:c>
+      <x:c r="B415" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C415" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D415" s="2" t="s">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:4">
+      <x:c r="A416" s="1">
+        <x:v>45818.8489649653</x:v>
+      </x:c>
+      <x:c r="B416" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C416" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D416" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:4">
+      <x:c r="A417" s="1">
+        <x:v>45818.8701341667</x:v>
+      </x:c>
+      <x:c r="B417" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C417" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D417" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:4">
+      <x:c r="A418" s="1">
+        <x:v>45818.8701343403</x:v>
+      </x:c>
+      <x:c r="B418" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C418" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D418" s="2" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:4">
+      <x:c r="A419" s="1">
+        <x:v>45818.9129159375</x:v>
+      </x:c>
+      <x:c r="B419" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C419" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D419" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:4">
+      <x:c r="A420" s="1">
+        <x:v>45818.9129161111</x:v>
+      </x:c>
+      <x:c r="B420" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C420" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D420" s="2" t="s">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:4">
+      <x:c r="A421" s="1">
+        <x:v>45818.913438588</x:v>
+      </x:c>
+      <x:c r="B421" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C421" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D421" s="2" t="s">
+        <x:v>210</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:4">
+      <x:c r="A422" s="1">
+        <x:v>45818.915431713</x:v>
+      </x:c>
+      <x:c r="B422" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C422" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D422" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:4">
+      <x:c r="A423" s="1">
+        <x:v>45818.915431875</x:v>
+      </x:c>
+      <x:c r="B423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C423" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D423" s="2" t="s">
+        <x:v>211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:4">
+      <x:c r="A424" s="1">
+        <x:v>45818.9241413194</x:v>
+      </x:c>
+      <x:c r="B424" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C424" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D424" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:4">
+      <x:c r="A425" s="1">
+        <x:v>45818.9241416551</x:v>
+      </x:c>
+      <x:c r="B425" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C425" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D425" s="2" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
+++ b/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
@@ -982,6 +982,66 @@
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>打开文件失败：H5509_alarm.xlsx，详细信息：未能找到文件“D:\GitHub\H5509_V2\bin\Debug\H5509_alarm.xlsx”。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:17:00]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:18:00]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:18:50]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:26:23]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:28:29]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:36:54]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:41:16]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 16:54:32]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-12 22:29:57]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：SELECT * FROM dut_ZRS240929001A_20250607_10_23_42，错误信息：对象名 'dut_ZRS240929001A_20250607_10_23_42' 无效。</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -7296,6 +7356,650 @@
         <x:v>212</x:v>
       </x:c>
     </x:row>
+    <x:row r="426" spans="1:4">
+      <x:c r="A426" s="1">
+        <x:v>45820.6781417477</x:v>
+      </x:c>
+      <x:c r="B426" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C426" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D426" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:4">
+      <x:c r="A427" s="1">
+        <x:v>45820.6784817593</x:v>
+      </x:c>
+      <x:c r="B427" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C427" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D427" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:4">
+      <x:c r="A428" s="1">
+        <x:v>45820.6784819676</x:v>
+      </x:c>
+      <x:c r="B428" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C428" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D428" s="2" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:4">
+      <x:c r="A429" s="1">
+        <x:v>45820.6791690509</x:v>
+      </x:c>
+      <x:c r="B429" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C429" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D429" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:4">
+      <x:c r="A430" s="1">
+        <x:v>45820.6791692361</x:v>
+      </x:c>
+      <x:c r="B430" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C430" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D430" s="2" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:4">
+      <x:c r="A431" s="1">
+        <x:v>45820.679756412</x:v>
+      </x:c>
+      <x:c r="B431" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C431" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D431" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:4">
+      <x:c r="A432" s="1">
+        <x:v>45820.679756956</x:v>
+      </x:c>
+      <x:c r="B432" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C432" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D432" s="2" t="s">
+        <x:v>216</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:4">
+      <x:c r="A433" s="1">
+        <x:v>45820.684992963</x:v>
+      </x:c>
+      <x:c r="B433" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C433" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D433" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:4">
+      <x:c r="A434" s="1">
+        <x:v>45820.6849931366</x:v>
+      </x:c>
+      <x:c r="B434" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C434" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D434" s="2" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" spans="1:4">
+      <x:c r="A435" s="1">
+        <x:v>45820.6864526273</x:v>
+      </x:c>
+      <x:c r="B435" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C435" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D435" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" spans="1:4">
+      <x:c r="A436" s="1">
+        <x:v>45820.6864528472</x:v>
+      </x:c>
+      <x:c r="B436" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C436" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D436" s="2" t="s">
+        <x:v>218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" spans="1:4">
+      <x:c r="A437" s="1">
+        <x:v>45820.6922994676</x:v>
+      </x:c>
+      <x:c r="B437" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C437" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D437" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" spans="1:4">
+      <x:c r="A438" s="1">
+        <x:v>45820.6922996528</x:v>
+      </x:c>
+      <x:c r="B438" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C438" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D438" s="2" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" spans="1:4">
+      <x:c r="A439" s="1">
+        <x:v>45820.6953343056</x:v>
+      </x:c>
+      <x:c r="B439" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C439" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D439" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" spans="1:4">
+      <x:c r="A440" s="1">
+        <x:v>45820.6953344676</x:v>
+      </x:c>
+      <x:c r="B440" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C440" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D440" s="2" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" spans="1:4">
+      <x:c r="A441" s="1">
+        <x:v>45820.7045464583</x:v>
+      </x:c>
+      <x:c r="B441" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C441" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D441" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" spans="1:4">
+      <x:c r="A442" s="1">
+        <x:v>45820.7045466204</x:v>
+      </x:c>
+      <x:c r="B442" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C442" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D442" s="2" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" spans="1:4">
+      <x:c r="A443" s="1">
+        <x:v>45820.9374696759</x:v>
+      </x:c>
+      <x:c r="B443" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C443" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D443" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" spans="1:4">
+      <x:c r="A444" s="1">
+        <x:v>45820.9374696991</x:v>
+      </x:c>
+      <x:c r="B444" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C444" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D444" s="2" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" spans="1:4">
+      <x:c r="A445" s="1">
+        <x:v>45820.9378777662</x:v>
+      </x:c>
+      <x:c r="B445" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C445" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D445" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" spans="1:4">
+      <x:c r="A446" s="1">
+        <x:v>45820.9378830903</x:v>
+      </x:c>
+      <x:c r="B446" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C446" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D446" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:4">
+      <x:c r="A447" s="1">
+        <x:v>45820.9379101505</x:v>
+      </x:c>
+      <x:c r="B447" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C447" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D447" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" spans="1:4">
+      <x:c r="A448" s="1">
+        <x:v>45820.9379161806</x:v>
+      </x:c>
+      <x:c r="B448" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C448" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D448" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" spans="1:4">
+      <x:c r="A449" s="1">
+        <x:v>45820.9379209144</x:v>
+      </x:c>
+      <x:c r="B449" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C449" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D449" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" spans="1:4">
+      <x:c r="A450" s="1">
+        <x:v>45820.9380037616</x:v>
+      </x:c>
+      <x:c r="B450" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C450" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D450" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" spans="1:4">
+      <x:c r="A451" s="1">
+        <x:v>45820.9380220255</x:v>
+      </x:c>
+      <x:c r="B451" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C451" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D451" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" spans="1:4">
+      <x:c r="A452" s="1">
+        <x:v>45820.9380269097</x:v>
+      </x:c>
+      <x:c r="B452" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C452" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D452" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" spans="1:4">
+      <x:c r="A453" s="1">
+        <x:v>45820.9380495139</x:v>
+      </x:c>
+      <x:c r="B453" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C453" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D453" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" spans="1:4">
+      <x:c r="A454" s="1">
+        <x:v>45820.9380586458</x:v>
+      </x:c>
+      <x:c r="B454" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C454" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D454" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" spans="1:4">
+      <x:c r="A455" s="1">
+        <x:v>45820.9380722685</x:v>
+      </x:c>
+      <x:c r="B455" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C455" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D455" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" spans="1:4">
+      <x:c r="A456" s="1">
+        <x:v>45820.9380816435</x:v>
+      </x:c>
+      <x:c r="B456" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C456" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D456" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" spans="1:4">
+      <x:c r="A457" s="1">
+        <x:v>45820.9380816667</x:v>
+      </x:c>
+      <x:c r="B457" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C457" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D457" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" spans="1:4">
+      <x:c r="A458" s="1">
+        <x:v>45820.9380816898</x:v>
+      </x:c>
+      <x:c r="B458" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C458" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D458" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" spans="1:4">
+      <x:c r="A459" s="1">
+        <x:v>45820.938081713</x:v>
+      </x:c>
+      <x:c r="B459" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C459" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D459" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" spans="1:4">
+      <x:c r="A460" s="1">
+        <x:v>45820.9381063079</x:v>
+      </x:c>
+      <x:c r="B460" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C460" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D460" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" spans="1:4">
+      <x:c r="A461" s="1">
+        <x:v>45820.938106331</x:v>
+      </x:c>
+      <x:c r="B461" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C461" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D461" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:4">
+      <x:c r="A462" s="1">
+        <x:v>45820.9381063542</x:v>
+      </x:c>
+      <x:c r="B462" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C462" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D462" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" spans="1:4">
+      <x:c r="A463" s="1">
+        <x:v>45820.9381063889</x:v>
+      </x:c>
+      <x:c r="B463" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C463" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D463" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" spans="1:4">
+      <x:c r="A464" s="1">
+        <x:v>45820.9381132986</x:v>
+      </x:c>
+      <x:c r="B464" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C464" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D464" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" spans="1:4">
+      <x:c r="A465" s="1">
+        <x:v>45820.9381133333</x:v>
+      </x:c>
+      <x:c r="B465" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C465" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D465" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" spans="1:4">
+      <x:c r="A466" s="1">
+        <x:v>45820.9381133681</x:v>
+      </x:c>
+      <x:c r="B466" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C466" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D466" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" spans="1:4">
+      <x:c r="A467" s="1">
+        <x:v>45820.9381133912</x:v>
+      </x:c>
+      <x:c r="B467" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C467" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D467" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:4">
+      <x:c r="A468" s="1">
+        <x:v>45820.9381792824</x:v>
+      </x:c>
+      <x:c r="B468" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C468" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D468" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" spans="1:4">
+      <x:c r="A469" s="1">
+        <x:v>45820.9381793056</x:v>
+      </x:c>
+      <x:c r="B469" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C469" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D469" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" spans="1:4">
+      <x:c r="A470" s="1">
+        <x:v>45820.9381793403</x:v>
+      </x:c>
+      <x:c r="B470" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C470" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D470" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" spans="1:4">
+      <x:c r="A471" s="1">
+        <x:v>45820.938179375</x:v>
+      </x:c>
+      <x:c r="B471" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C471" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D471" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
+++ b/bin/Debug/Logs/202506/Log_20250605-205714.xlsx
@@ -1042,6 +1042,135 @@
   </x:si>
   <x:si>
     <x:t>命令：SELECT * FROM dut_ZRS240929001A_20250607_10_23_42，错误信息：对象名 'dut_ZRS240929001A_20250607_10_23_42' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 09:19:45]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 09:34:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>密码错误！</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 09:37:28]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 09:39:14]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 09:56:43]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:00:20]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:03:11]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:11:46]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:Tray名称:8x19_UFS-&gt;8x19_eMMC:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:Tray名称:8x19_eMMC-&gt;8x19_UFS:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:18:52]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:19:43]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:20:57]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:27:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:28:20]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-19 10:31:14]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-20 08:55:08]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-20 11:01:03]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-20 11:46:39]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-20 15:36:20]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-20 20:00:04]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-06-20 20:48:42]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -8000,6 +8129,650 @@
         <x:v>169</x:v>
       </x:c>
     </x:row>
+    <x:row r="472" spans="1:4">
+      <x:c r="A472" s="1">
+        <x:v>45827.3887170255</x:v>
+      </x:c>
+      <x:c r="B472" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C472" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D472" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" spans="1:4">
+      <x:c r="A473" s="1">
+        <x:v>45827.3887172569</x:v>
+      </x:c>
+      <x:c r="B473" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C473" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D473" s="2" t="s">
+        <x:v>224</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" spans="1:4">
+      <x:c r="A474" s="1">
+        <x:v>45827.3988383912</x:v>
+      </x:c>
+      <x:c r="B474" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C474" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D474" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" spans="1:4">
+      <x:c r="A475" s="1">
+        <x:v>45827.3988385764</x:v>
+      </x:c>
+      <x:c r="B475" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C475" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D475" s="2" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" spans="1:4">
+      <x:c r="A476" s="1">
+        <x:v>45827.3992493634</x:v>
+      </x:c>
+      <x:c r="B476" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C476" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D476" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" spans="1:4">
+      <x:c r="A477" s="1">
+        <x:v>45827.4010237963</x:v>
+      </x:c>
+      <x:c r="B477" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C477" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D477" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" spans="1:4">
+      <x:c r="A478" s="1">
+        <x:v>45827.4010239931</x:v>
+      </x:c>
+      <x:c r="B478" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C478" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D478" s="2" t="s">
+        <x:v>227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" spans="1:4">
+      <x:c r="A479" s="1">
+        <x:v>45827.4022473148</x:v>
+      </x:c>
+      <x:c r="B479" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C479" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D479" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" spans="1:4">
+      <x:c r="A480" s="1">
+        <x:v>45827.4022474768</x:v>
+      </x:c>
+      <x:c r="B480" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C480" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D480" s="2" t="s">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" spans="1:4">
+      <x:c r="A481" s="1">
+        <x:v>45827.414396875</x:v>
+      </x:c>
+      <x:c r="B481" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C481" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D481" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" spans="1:4">
+      <x:c r="A482" s="1">
+        <x:v>45827.4143971759</x:v>
+      </x:c>
+      <x:c r="B482" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C482" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D482" s="2" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" spans="1:4">
+      <x:c r="A483" s="1">
+        <x:v>45827.4168997338</x:v>
+      </x:c>
+      <x:c r="B483" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C483" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D483" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" spans="1:4">
+      <x:c r="A484" s="1">
+        <x:v>45827.416899919</x:v>
+      </x:c>
+      <x:c r="B484" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C484" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D484" s="2" t="s">
+        <x:v>230</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" spans="1:4">
+      <x:c r="A485" s="1">
+        <x:v>45827.4188818056</x:v>
+      </x:c>
+      <x:c r="B485" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C485" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D485" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" spans="1:4">
+      <x:c r="A486" s="1">
+        <x:v>45827.4188821875</x:v>
+      </x:c>
+      <x:c r="B486" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C486" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D486" s="2" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" spans="1:4">
+      <x:c r="A487" s="1">
+        <x:v>45827.4248386574</x:v>
+      </x:c>
+      <x:c r="B487" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C487" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D487" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" spans="1:4">
+      <x:c r="A488" s="1">
+        <x:v>45827.4248388194</x:v>
+      </x:c>
+      <x:c r="B488" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C488" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D488" s="2" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" spans="1:4">
+      <x:c r="A489" s="1">
+        <x:v>45827.4258090046</x:v>
+      </x:c>
+      <x:c r="B489" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C489" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D489" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" spans="1:4">
+      <x:c r="A490" s="1">
+        <x:v>45827.4260422569</x:v>
+      </x:c>
+      <x:c r="B490" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C490" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D490" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" spans="1:4">
+      <x:c r="A491" s="1">
+        <x:v>45827.4297763426</x:v>
+      </x:c>
+      <x:c r="B491" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C491" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D491" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" spans="1:4">
+      <x:c r="A492" s="1">
+        <x:v>45827.4297765046</x:v>
+      </x:c>
+      <x:c r="B492" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C492" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D492" s="2" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" spans="1:4">
+      <x:c r="A493" s="1">
+        <x:v>45827.4303690509</x:v>
+      </x:c>
+      <x:c r="B493" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C493" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D493" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" spans="1:4">
+      <x:c r="A494" s="1">
+        <x:v>45827.430369213</x:v>
+      </x:c>
+      <x:c r="B494" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C494" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D494" s="2" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" spans="1:4">
+      <x:c r="A495" s="1">
+        <x:v>45827.4308409143</x:v>
+      </x:c>
+      <x:c r="B495" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C495" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D495" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:4">
+      <x:c r="A496" s="1">
+        <x:v>45827.4312262731</x:v>
+      </x:c>
+      <x:c r="B496" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C496" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D496" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:4">
+      <x:c r="A497" s="1">
+        <x:v>45827.4312264583</x:v>
+      </x:c>
+      <x:c r="B497" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C497" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D497" s="2" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" spans="1:4">
+      <x:c r="A498" s="1">
+        <x:v>45827.431623044</x:v>
+      </x:c>
+      <x:c r="B498" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C498" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D498" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:4">
+      <x:c r="A499" s="1">
+        <x:v>45827.4356401968</x:v>
+      </x:c>
+      <x:c r="B499" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C499" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D499" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:4">
+      <x:c r="A500" s="1">
+        <x:v>45827.4356407755</x:v>
+      </x:c>
+      <x:c r="B500" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C500" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D500" s="2" t="s">
+        <x:v>238</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:4">
+      <x:c r="A501" s="1">
+        <x:v>45827.436346794</x:v>
+      </x:c>
+      <x:c r="B501" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C501" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D501" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:4">
+      <x:c r="A502" s="1">
+        <x:v>45827.436346956</x:v>
+      </x:c>
+      <x:c r="B502" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C502" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D502" s="2" t="s">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:4">
+      <x:c r="A503" s="1">
+        <x:v>45827.4372009606</x:v>
+      </x:c>
+      <x:c r="B503" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C503" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D503" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:4">
+      <x:c r="A504" s="1">
+        <x:v>45827.4383665625</x:v>
+      </x:c>
+      <x:c r="B504" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C504" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D504" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:4">
+      <x:c r="A505" s="1">
+        <x:v>45827.4383667477</x:v>
+      </x:c>
+      <x:c r="B505" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C505" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D505" s="2" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:4">
+      <x:c r="A506" s="1">
+        <x:v>45828.3716315046</x:v>
+      </x:c>
+      <x:c r="B506" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C506" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D506" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:4">
+      <x:c r="A507" s="1">
+        <x:v>45828.3716318403</x:v>
+      </x:c>
+      <x:c r="B507" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C507" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D507" s="2" t="s">
+        <x:v>241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:4">
+      <x:c r="A508" s="1">
+        <x:v>45828.4590635069</x:v>
+      </x:c>
+      <x:c r="B508" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C508" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D508" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:4">
+      <x:c r="A509" s="1">
+        <x:v>45828.4590636921</x:v>
+      </x:c>
+      <x:c r="B509" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C509" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D509" s="2" t="s">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:4">
+      <x:c r="A510" s="1">
+        <x:v>45828.4907356019</x:v>
+      </x:c>
+      <x:c r="B510" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C510" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D510" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:4">
+      <x:c r="A511" s="1">
+        <x:v>45828.4907358565</x:v>
+      </x:c>
+      <x:c r="B511" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C511" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D511" s="2" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:4">
+      <x:c r="A512" s="1">
+        <x:v>45828.6502334028</x:v>
+      </x:c>
+      <x:c r="B512" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C512" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D512" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:4">
+      <x:c r="A513" s="1">
+        <x:v>45828.6502335995</x:v>
+      </x:c>
+      <x:c r="B513" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C513" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D513" s="2" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:4">
+      <x:c r="A514" s="1">
+        <x:v>45828.8333874306</x:v>
+      </x:c>
+      <x:c r="B514" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C514" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D514" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:4">
+      <x:c r="A515" s="1">
+        <x:v>45828.8333876968</x:v>
+      </x:c>
+      <x:c r="B515" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C515" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D515" s="2" t="s">
+        <x:v>245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:4">
+      <x:c r="A516" s="1">
+        <x:v>45828.8671623032</x:v>
+      </x:c>
+      <x:c r="B516" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C516" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D516" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:4">
+      <x:c r="A517" s="1">
+        <x:v>45828.8671624537</x:v>
+      </x:c>
+      <x:c r="B517" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C517" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D517" s="2" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
